--- a/diseases/d237/2020-2025.xlsx
+++ b/diseases/d237/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>330</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>90.01292912982046</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>964</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>9.310693345795238</v>
       </c>
@@ -1806,9 +1800,6 @@
       <c r="O7" t="n">
         <v>836</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>8.074418710668899</v>
       </c>
@@ -2202,9 +2193,6 @@
       <c r="O9" t="n">
         <v>759</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>7.330722250475713</v>
       </c>
@@ -2598,9 +2586,6 @@
       <c r="O11" t="n">
         <v>618</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>5.968888472719355</v>
       </c>
@@ -2994,9 +2979,6 @@
       <c r="O13" t="n">
         <v>675</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>6.519417021174053</v>
       </c>
@@ -3390,9 +3372,6 @@
       <c r="O15" t="n">
         <v>561</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>5.418359924264657</v>
       </c>
@@ -3786,9 +3765,6 @@
       <c r="O17" t="n">
         <v>609</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>5.881962912437034</v>
       </c>
@@ -4182,9 +4158,6 @@
       <c r="O19" t="n">
         <v>632</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>6.104106010936298</v>
       </c>
@@ -4578,9 +4551,6 @@
       <c r="O21" t="n">
         <v>662</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>6.393857878544034</v>
       </c>
@@ -4974,9 +4944,6 @@
       <c r="O23" t="n">
         <v>686</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>6.625659372630222</v>
       </c>
@@ -5370,9 +5337,6 @@
       <c r="O25" t="n">
         <v>635</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>6.133081197697071</v>
       </c>
@@ -5766,9 +5730,6 @@
       <c r="O27" t="n">
         <v>594</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>5.737086978633166</v>
       </c>
@@ -6162,9 +6123,6 @@
       <c r="O29" t="n">
         <v>353</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>94.72860790541094</v>
       </c>
@@ -6807,9 +6765,6 @@
       <c r="O32" t="n">
         <v>569</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>5.462680650681109</v>
       </c>
@@ -7203,9 +7158,6 @@
       <c r="O34" t="n">
         <v>532</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>5.107462400988314</v>
       </c>
@@ -7599,9 +7551,6 @@
       <c r="O36" t="n">
         <v>604</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>5.798697913904025</v>
       </c>
@@ -7995,9 +7944,6 @@
       <c r="O38" t="n">
         <v>569</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>5.462680650681109</v>
       </c>
@@ -8391,9 +8337,6 @@
       <c r="O40" t="n">
         <v>530</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>5.088261414518432</v>
       </c>
@@ -8787,9 +8730,6 @@
       <c r="O42" t="n">
         <v>578</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>5.549085089795573</v>
       </c>
@@ -9183,9 +9123,6 @@
       <c r="O44" t="n">
         <v>596</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>5.721893968024501</v>
       </c>
@@ -9579,9 +9516,6 @@
       <c r="O46" t="n">
         <v>733</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>7.037161541211341</v>
       </c>
@@ -9975,9 +9909,6 @@
       <c r="O48" t="n">
         <v>821</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>7.882004945886099</v>
       </c>
@@ -10371,9 +10302,6 @@
       <c r="O50" t="n">
         <v>768</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>7.373178804434256</v>
       </c>
@@ -10767,9 +10695,6 @@
       <c r="O52" t="n">
         <v>787</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>7.555588175898125</v>
       </c>
@@ -11163,9 +11088,6 @@
       <c r="O54" t="n">
         <v>761</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>7.305975351789674</v>
       </c>
@@ -11559,9 +11481,6 @@
       <c r="O56" t="n">
         <v>371</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>97.54032740423105</v>
       </c>
@@ -11965,9 +11884,6 @@
       <c r="O58" t="n">
         <v>687</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>6.550756731593851</v>
       </c>
@@ -12361,9 +12277,6 @@
       <c r="O60" t="n">
         <v>669</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>6.379121184041175</v>
       </c>
@@ -12757,9 +12670,6 @@
       <c r="O62" t="n">
         <v>742</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>7.075198682449255</v>
       </c>
@@ -13153,9 +13063,6 @@
       <c r="O64" t="n">
         <v>666</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>6.350515259449061</v>
       </c>
@@ -13549,9 +13456,6 @@
       <c r="O66" t="n">
         <v>727</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>6.93216905948869</v>
       </c>
@@ -13945,9 +13849,6 @@
       <c r="O68" t="n">
         <v>776</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>7.399399161159867</v>
       </c>
@@ -14341,9 +14242,6 @@
       <c r="O70" t="n">
         <v>719</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>6.855886593909722</v>
       </c>
@@ -14737,9 +14635,6 @@
       <c r="O72" t="n">
         <v>906</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>8.638989226818092</v>
       </c>
@@ -15133,9 +15028,6 @@
       <c r="O74" t="n">
         <v>966</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>9.211107718660351</v>
       </c>
@@ -15529,9 +15421,6 @@
       <c r="O76" t="n">
         <v>936</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>8.925048472739222</v>
       </c>
@@ -15925,9 +15814,6 @@
       <c r="O78" t="n">
         <v>957</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>9.125289944884011</v>
       </c>
@@ -16321,9 +16207,6 @@
       <c r="O80" t="n">
         <v>852</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>8.12408258416006</v>
       </c>
@@ -16717,9 +16600,6 @@
       <c r="O82" t="n">
         <v>494</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>127.46495681286</v>
       </c>
@@ -17123,9 +17003,6 @@
       <c r="O84" t="n">
         <v>879</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>8.330573850489799</v>
       </c>
@@ -17519,9 +17396,6 @@
       <c r="O86" t="n">
         <v>790</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>7.487091401464096</v>
       </c>
@@ -17915,9 +17789,6 @@
       <c r="O88" t="n">
         <v>879</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>8.330573850489799</v>
       </c>
@@ -18311,9 +18182,6 @@
       <c r="O90" t="n">
         <v>725</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>6.871064893748696</v>
       </c>
@@ -18707,9 +18575,6 @@
       <c r="O92" t="n">
         <v>879</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>8.330573850489799</v>
       </c>
@@ -19103,9 +18968,6 @@
       <c r="O94" t="n">
         <v>800</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>7.581864710343388</v>
       </c>
@@ -19499,9 +19361,6 @@
       <c r="O96" t="n">
         <v>841</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>7.970435276748487</v>
       </c>
@@ -19895,9 +19754,6 @@
       <c r="O98" t="n">
         <v>1066</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>10.10283472653257</v>
       </c>
@@ -20291,9 +20147,6 @@
       <c r="O100" t="n">
         <v>1053</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>9.979629424989485</v>
       </c>
@@ -20687,9 +20540,6 @@
       <c r="O102" t="n">
         <v>1103</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>10.45349596938595</v>
       </c>
@@ -21083,9 +20933,6 @@
       <c r="O104" t="n">
         <v>943</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>8.93712302731727</v>
       </c>
@@ -21479,9 +21326,6 @@
       <c r="O106" t="n">
         <v>933</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>8.842349718437976</v>
       </c>
@@ -21875,9 +21719,6 @@
       <c r="O108" t="n">
         <v>544</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>138.2832289642357</v>
       </c>
@@ -22281,9 +22122,6 @@
       <c r="O110" t="n">
         <v>969</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>9.135477433343777</v>
       </c>
@@ -22677,9 +22515,6 @@
       <c r="O112" t="n">
         <v>920</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>8.673518306167466</v>
       </c>
@@ -23073,9 +22908,6 @@
       <c r="O114" t="n">
         <v>933</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>8.796078890928527</v>
       </c>
@@ -23469,9 +23301,6 @@
       <c r="O116" t="n">
         <v>930</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>8.76779567906059</v>
       </c>
@@ -23865,9 +23694,6 @@
       <c r="O118" t="n">
         <v>1001</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>9.437165026601775</v>
       </c>
@@ -24261,9 +24087,6 @@
       <c r="O120" t="n">
         <v>860</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>8.107854068808718</v>
       </c>
@@ -24657,9 +24480,6 @@
       <c r="O122" t="n">
         <v>1054</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>9.936835102935335</v>
       </c>
@@ -25053,9 +24873,6 @@
       <c r="O124" t="n">
         <v>1202</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>11.33214022175358</v>
       </c>
@@ -25449,9 +25266,6 @@
       <c r="O126" t="n">
         <v>1245</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>11.73753292519402</v>
       </c>
@@ -25845,9 +25659,6 @@
       <c r="O128" t="n">
         <v>1270</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>11.97322635742683</v>
       </c>
@@ -26241,9 +26052,6 @@
       <c r="O130" t="n">
         <v>1105</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>10.41764970469027</v>
       </c>
@@ -26637,9 +26445,6 @@
       <c r="O132" t="n">
         <v>1036</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>9.767135831727712</v>
       </c>
@@ -27033,9 +26838,6 @@
       <c r="O134" t="n">
         <v>649</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>162.9564160636359</v>
       </c>
@@ -27439,9 +27241,6 @@
       <c r="O136" t="n">
         <v>1161</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>10.89462309530599</v>
       </c>
@@ -27835,9 +27634,6 @@
       <c r="O138" t="n">
         <v>1012</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>9.496432878940281</v>
       </c>
@@ -28231,9 +28027,6 @@
       <c r="O140" t="n">
         <v>1079</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>10.12514928495708</v>
       </c>
@@ -28627,9 +28420,6 @@
       <c r="O142" t="n">
         <v>1013</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>9.505816705895755</v>
       </c>
@@ -29023,9 +28813,6 @@
       <c r="O144" t="n">
         <v>1047</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>9.824866822381891</v>
       </c>
@@ -29419,9 +29206,6 @@
       <c r="O146" t="n">
         <v>991</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>9.299372512875314</v>
       </c>
@@ -29815,9 +29599,6 @@
       <c r="O148" t="n">
         <v>1080</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>10.13453311191255</v>
       </c>
@@ -30211,9 +29992,6 @@
       <c r="O150" t="n">
         <v>1212</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>11.3731982700352</v>
       </c>
@@ -30607,9 +30385,6 @@
       <c r="O152" t="n">
         <v>1314</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>12.3303486194936</v>
       </c>
@@ -31003,9 +30778,6 @@
       <c r="O154" t="n">
         <v>1315</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>12.33973244644908</v>
       </c>
@@ -31399,9 +31171,6 @@
       <c r="O156" t="n">
         <v>1136</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>10.66002742141913</v>
       </c>
@@ -31794,9 +31563,6 @@
       </c>
       <c r="O158" t="n">
         <v>1162</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>10.90400692226147</v>
